--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. ZARAGOZA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. ZARAGOZA.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4768</v>
+        <v>4.4451</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2864</v>
+        <v>2.5266</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1905</v>
+        <v>1.9186</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1374</v>
+        <v>2.1273</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2171</v>
+        <v>4.210800000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.0798</v>
+        <v>-2.0835</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7036</v>
+        <v>3.8473</v>
       </c>
       <c r="K2" t="n">
-        <v>4.525300000000001</v>
+        <v>4.6207</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8217999999999999</v>
+        <v>-0.7733</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5662</v>
+        <v>-1.7201</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3082</v>
+        <v>-0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.258</v>
+        <v>-1.3101</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R2" t="n">
-        <v>3.8921</v>
+        <v>3.8466</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01180000000000003</v>
+        <v>-0.006000000000000005</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.09489999999999998</v>
+        <v>-0.04900000000000015</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1066</v>
+        <v>0.04300000000000004</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7262000000000001</v>
+        <v>0.7527999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="3">
@@ -643,28 +643,28 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4637</v>
+        <v>1.4816</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4637</v>
+        <v>1.4816</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4637</v>
+        <v>1.4816</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4637</v>
+        <v>1.4816</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4637</v>
+        <v>1.4816</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4637</v>
+        <v>1.4816</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -721,28 +721,28 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1625000000000005</v>
+        <v>-0.1066000000000003</v>
       </c>
       <c r="E5" t="n">
-        <v>1.974</v>
+        <v>2.2594</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1364</v>
+        <v>-2.366</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7264999999999999</v>
+        <v>0.7395</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3223</v>
+        <v>-2.3508</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0487</v>
+        <v>3.0904</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7847</v>
+        <v>2.9493</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4530999999999999</v>
+        <v>-0.3793</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2378</v>
+        <v>3.3287</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0581</v>
+        <v>-2.2097</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8691</v>
+        <v>-1.9715</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1889999999999999</v>
+        <v>-0.2382</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2049000000000001</v>
+        <v>0.2023999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2775</v>
+        <v>-3.2393</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4824</v>
+        <v>3.4417</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.4431</v>
+        <v>-3.4032</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3169</v>
+        <v>-1.2722</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.1262</v>
+        <v>-2.131</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3493</v>
+        <v>2.3546</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7839</v>
+        <v>3.8215</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4346</v>
+        <v>-1.4669</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1635000000000001</v>
+        <v>-0.2034000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.7166</v>
+        <v>-2.6591</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5531</v>
+        <v>2.4557</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3666</v>
+        <v>-0.4018999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3347</v>
+        <v>1.3061</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7012</v>
+        <v>-1.7081</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2101</v>
+        <v>-1.1863</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7221</v>
+        <v>0.7309</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9322</v>
+        <v>-1.9172</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8436</v>
+        <v>0.7844</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6127</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.231</v>
+        <v>0.2093</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4357</v>
+        <v>-1.4211</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5065</v>
+        <v>-1.4727</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07069999999999999</v>
+        <v>0.0517</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,58 +955,58 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2377</v>
+        <v>-1.281</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9334</v>
+        <v>-0.8305</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3043</v>
+        <v>-0.4506</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2503</v>
+        <v>-0.2938000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4966</v>
+        <v>1.4832</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7469</v>
+        <v>-1.7771</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5234</v>
+        <v>1.5801</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9436</v>
+        <v>1.9939</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4201</v>
+        <v>-0.4137999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7737</v>
+        <v>-1.8739</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.447</v>
+        <v>-0.5106999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3267</v>
+        <v>-1.3633</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0484</v>
+        <v>2.0246</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7825000000000001</v>
+        <v>-0.7847</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2035</v>
+        <v>-0.1837</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.6011</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6444</v>
+        <v>-1.6505</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5283</v>
+        <v>-0.3066</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1161</v>
+        <v>-1.3439</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5256</v>
+        <v>3.4915</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9866</v>
+        <v>1.9396</v>
       </c>
       <c r="I8" t="n">
-        <v>1.539</v>
+        <v>1.5519</v>
       </c>
       <c r="J8" t="n">
-        <v>5.9754</v>
+        <v>6.0909</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0158</v>
+        <v>2.0538</v>
       </c>
       <c r="L8" t="n">
-        <v>3.9596</v>
+        <v>4.037</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4498</v>
+        <v>-2.5994</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0292</v>
+        <v>-0.1142</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4205</v>
+        <v>-2.4851</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0969</v>
+        <v>-4.0491</v>
       </c>
       <c r="R8" t="n">
-        <v>3.6872</v>
+        <v>3.6442</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.4617</v>
+        <v>-3.4279</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.4067</v>
+        <v>-2.3485</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0549</v>
+        <v>-1.0794</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2987</v>
+        <v>-1.3092</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2987</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1515</v>
+        <v>-3.0988</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2371</v>
+        <v>-2.0208</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9144</v>
+        <v>-1.078</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7883</v>
+        <v>-3.7715</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2734999999999999</v>
+        <v>0.2954000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.0618</v>
+        <v>-4.0669</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9914000000000001</v>
+        <v>-0.861</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2779</v>
+        <v>1.3598</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2693</v>
+        <v>-2.2208</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7969</v>
+        <v>-2.9105</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0043</v>
+        <v>-1.0643</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7925</v>
+        <v>-1.8461</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R9" t="n">
-        <v>3.0727</v>
+        <v>3.0368</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02870000000000006</v>
+        <v>0.03900000000000003</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1008</v>
+        <v>1.1242</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0721</v>
+        <v>-1.0853</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6081000000000001</v>
+        <v>0.6337999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7262000000000001</v>
+        <v>0.7527999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1581</v>
+        <v>-4.2745</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1243</v>
+        <v>-1.0201</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0339</v>
+        <v>-3.2543</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.0527</v>
+        <v>-5.1072</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0851</v>
+        <v>-2.0948</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9677</v>
+        <v>-3.0123</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2426</v>
+        <v>-1.1839</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7183999999999999</v>
+        <v>-0.6743</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5242</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.8101</v>
+        <v>-3.9233</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3666</v>
+        <v>-1.4205</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4434</v>
+        <v>-2.5028</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R10" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2062</v>
+        <v>3.1781</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3717</v>
+        <v>2.3907</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8346</v>
+        <v>0.7874</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7213</v>
+        <v>-2.7504</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7213</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0693</v>
+        <v>-6.046799999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8981</v>
+        <v>-4.6815</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1711</v>
+        <v>-1.3654</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7714</v>
+        <v>-0.7968</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7365</v>
+        <v>-1.7394</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9651000000000001</v>
+        <v>0.9426</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7323</v>
+        <v>1.8294</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.258</v>
+        <v>-0.1818</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9902</v>
+        <v>2.0112</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5037</v>
+        <v>-2.6263</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4785</v>
+        <v>-1.5576</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0251</v>
+        <v>-1.0687</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0727</v>
+        <v>3.0368</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6192</v>
+        <v>-1.6004</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1776</v>
+        <v>-1.1338</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4415</v>
+        <v>-0.4666</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4496</v>
+        <v>-2.4349</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.1509</v>
+        <v>-1.1257</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2987</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0617</v>
+        <v>-7.03</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.701600000000001</v>
+        <v>-7.5925</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6399</v>
+        <v>0.5625</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.779</v>
+        <v>-5.7367</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.079</v>
+        <v>-2.057</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.7</v>
+        <v>-3.6798</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.8181</v>
+        <v>-6.7375</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.1658</v>
+        <v>-3.1253</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.6524</v>
+        <v>-3.6123</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0391</v>
+        <v>1.0007</v>
       </c>
       <c r="N12" t="n">
-        <v>1.0868</v>
+        <v>1.0683</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.04770000000000001</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6387</v>
+        <v>1.6197</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2939</v>
+        <v>-1.2694</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6787000000000001</v>
+        <v>-0.6526000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6153</v>
+        <v>-0.6168</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.9252</v>
+        <v>-9.891500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7394</v>
+        <v>-5.5131</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.1858</v>
+        <v>-4.3784</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.132099999999999</v>
+        <v>-4.1495</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8918999999999999</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.2402</v>
+        <v>-3.2599</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9774999999999998</v>
+        <v>-0.8665999999999998</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3079999999999998</v>
+        <v>0.3911</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2855</v>
+        <v>-1.2577</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1546</v>
+        <v>-3.283</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2807</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.9548</v>
+        <v>-2.0022</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.6631</v>
+        <v>-2.6318</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1914</v>
+        <v>-2.1708</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0634</v>
+        <v>-1.0264</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1281</v>
+        <v>-1.1444</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9384999999999999</v>
+        <v>-0.9393000000000002</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.3407</v>
+        <v>-27.3601</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.862</v>
+        <v>-18.0603</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.478499999999999</v>
+        <v>-9.299800000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.9945</v>
+        <v>-12.1212</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9501</v>
+        <v>1.881400000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.9448</v>
+        <v>-14.0027</v>
       </c>
       <c r="J14" t="n">
-        <v>6.2361</v>
+        <v>7.239600000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.953800000000002</v>
+        <v>8.567400000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.7179</v>
+        <v>-1.3278</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.2304</v>
+        <v>-19.3611</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.0032</v>
+        <v>-6.6861</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.2267</v>
+        <v>-12.6748</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q14" t="n">
-        <v>-26.63</v>
+        <v>-26.319</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6542</v>
+        <v>27.3313</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.9808</v>
+        <v>-10.8664</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.9757</v>
+        <v>-4.624000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.0053</v>
+        <v>-6.242499999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.3893</v>
+        <v>-5.3846</v>
       </c>
       <c r="W14" t="n">
-        <v>5.508100000000001</v>
+        <v>5.6425</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.8974</v>
+        <v>-11.0271</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. ZARAGOZA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. ZARAGOZA.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4451</v>
+        <v>3.3335</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5266</v>
+        <v>2.1754</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9186</v>
+        <v>1.1581</v>
       </c>
       <c r="G2" t="n">
         <v>2.1273</v>
@@ -610,13 +610,13 @@
         <v>3.8466</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.006000000000000005</v>
+        <v>-1.1177</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.04900000000000015</v>
+        <v>-0.4003</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04300000000000004</v>
+        <v>-0.7173999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.5019</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2963</v>
+        <v>1.0361</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2963</v>
+        <v>2.4913</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.4552</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2963</v>
+        <v>0.7395</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2963</v>
+        <v>-2.3508</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3.0904</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2963</v>
+        <v>2.9493</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2963</v>
+        <v>-0.3793</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.3287</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-2.2097</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.9715</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.2382</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.2023999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.2393</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.4417</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2.2606</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-1.0403</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-1.2203</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.3546</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.8215</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.4669</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1066000000000003</v>
+        <v>0.3737999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2594</v>
+        <v>-2.2836</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.366</v>
+        <v>2.6574</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7395</v>
+        <v>-0.4018999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3508</v>
+        <v>1.3061</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0904</v>
+        <v>-1.7081</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9493</v>
+        <v>-1.1863</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3793</v>
+        <v>0.7309</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3287</v>
+        <v>-1.9172</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2097</v>
+        <v>0.7844</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9715</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2382</v>
+        <v>0.2093</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2023999999999999</v>
+        <v>1.6196</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2393</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4417</v>
+        <v>1.6196</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.4032</v>
+        <v>-0.8439000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2722</v>
+        <v>-1.0973</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.131</v>
+        <v>0.2534</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3546</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.8215</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4669</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,61 +874,61 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2034000000000001</v>
+        <v>0.2963</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6591</v>
+        <v>0.2963</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4557</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4018999999999999</v>
+        <v>0.2963</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3061</v>
+        <v>0.2963</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7081</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1863</v>
+        <v>0.2963</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7309</v>
+        <v>0.2963</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9172</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7844</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5750999999999999</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2093</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6196</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6196</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4211</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4727</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0517</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MUNOZ SAMATAN</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.281</v>
+        <v>0.2301</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8305</v>
+        <v>1.3146</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4506</v>
+        <v>-1.0846</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2938000000000001</v>
+        <v>3.4915</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4832</v>
+        <v>1.9396</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7771</v>
+        <v>1.5519</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5801</v>
+        <v>6.0909</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9939</v>
+        <v>2.0538</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4137999999999999</v>
+        <v>4.037</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8739</v>
+        <v>-2.5994</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5106999999999999</v>
+        <v>-0.1142</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3633</v>
+        <v>-2.4851</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2025</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.227</v>
+        <v>-4.0491</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0246</v>
+        <v>3.6442</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7847</v>
+        <v>-1.5473</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1837</v>
+        <v>-0.7273000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6011</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.3092</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>D. MUNOZ SAMATAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6505</v>
+        <v>-0.9053999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3066</v>
+        <v>-0.5588000000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3439</v>
+        <v>-0.3466000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4915</v>
+        <v>-0.2938000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9396</v>
+        <v>1.4832</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5519</v>
+        <v>-1.7771</v>
       </c>
       <c r="J8" t="n">
-        <v>6.0909</v>
+        <v>1.5801</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0538</v>
+        <v>1.9939</v>
       </c>
       <c r="L8" t="n">
-        <v>4.037</v>
+        <v>-0.4137999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5994</v>
+        <v>-1.8739</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1142</v>
+        <v>-0.5106999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4851</v>
+        <v>-1.3633</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4049</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0491</v>
+        <v>-2.227</v>
       </c>
       <c r="R8" t="n">
-        <v>3.6442</v>
+        <v>2.0246</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.4279</v>
+        <v>-0.4092</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.3485</v>
+        <v>0.08800000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0794</v>
+        <v>-0.4972</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3092</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0988</v>
+        <v>-3.3758</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0208</v>
+        <v>-2.7474</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.078</v>
+        <v>-0.6283</v>
       </c>
       <c r="G9" t="n">
         <v>-3.7715</v>
@@ -1156,13 +1156,13 @@
         <v>3.0368</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03900000000000003</v>
+        <v>-0.2379999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1242</v>
+        <v>0.3976</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0853</v>
+        <v>-0.6355</v>
       </c>
       <c r="V9" t="n">
         <v>0.6337999999999999</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2745</v>
+        <v>-5.4055</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0201</v>
+        <v>-4.345800000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2543</v>
+        <v>-1.0597</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.1072</v>
+        <v>-0.7968</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0948</v>
+        <v>-1.7394</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0123</v>
+        <v>0.9426</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1839</v>
+        <v>1.8294</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6743</v>
+        <v>-0.1818</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5096000000000001</v>
+        <v>2.0112</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.9233</v>
+        <v>-2.6263</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4205</v>
+        <v>-1.5576</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5028</v>
+        <v>-1.0687</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4049</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.227</v>
+        <v>-4.2515</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6319</v>
+        <v>3.0368</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1781</v>
+        <v>-0.9591000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3907</v>
+        <v>-0.7981</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7874</v>
+        <v>-0.161</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7504</v>
+        <v>-2.4349</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.1257</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7504</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.046799999999999</v>
+        <v>-6.1826</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6815</v>
+        <v>-7.177300000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3654</v>
+        <v>0.9947</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7968</v>
+        <v>-5.7367</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7394</v>
+        <v>-2.057</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9426</v>
+        <v>-3.6798</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8294</v>
+        <v>-6.7375</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1818</v>
+        <v>-3.1253</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0112</v>
+        <v>-3.6123</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6263</v>
+        <v>1.0007</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5576</v>
+        <v>1.0683</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0687</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2147</v>
+        <v>1.4172</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.2515</v>
+        <v>-0.2025</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0368</v>
+        <v>1.6197</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6004</v>
+        <v>-0.4218</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1338</v>
+        <v>-0.2373</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4666</v>
+        <v>-0.1845</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4349</v>
+        <v>-1.4411</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.1257</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3092</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.03</v>
+        <v>-6.816800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.5925</v>
+        <v>-2.9285</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5625</v>
+        <v>-3.8883</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.7367</v>
+        <v>-5.1072</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.057</v>
+        <v>-2.0948</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.6798</v>
+        <v>-3.0123</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.7375</v>
+        <v>-1.1839</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.1253</v>
+        <v>-0.6743</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.6123</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0007</v>
+        <v>-3.9233</v>
       </c>
       <c r="N12" t="n">
-        <v>1.0683</v>
+        <v>-1.4205</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-2.5028</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4172</v>
+        <v>0.4049</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2025</v>
+        <v>-2.227</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6197</v>
+        <v>2.6319</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2694</v>
+        <v>0.6358</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6526000000000001</v>
+        <v>0.4823</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6168</v>
+        <v>0.1535</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4411</v>
+        <v>-2.7504</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4411</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.891500000000001</v>
+        <v>-9.400799999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.5131</v>
+        <v>-5.1376</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.3784</v>
+        <v>-4.263199999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-4.1495</v>
@@ -1468,13 +1468,13 @@
         <v>2.4294</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1708</v>
+        <v>-1.68</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0264</v>
+        <v>-0.6509</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1444</v>
+        <v>-1.0291</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9393000000000002</v>
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.3601</v>
+        <v>-25.3355</v>
       </c>
       <c r="E14" t="n">
-        <v>-18.0603</v>
+        <v>-17.4198</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.299800000000001</v>
+        <v>-7.915699999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-12.1212</v>
@@ -1519,10 +1519,10 @@
         <v>-14.0027</v>
       </c>
       <c r="J14" t="n">
-        <v>7.239600000000001</v>
+        <v>7.239599999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>8.567400000000001</v>
+        <v>8.567399999999999</v>
       </c>
       <c r="L14" t="n">
         <v>-1.3278</v>
@@ -1543,16 +1543,16 @@
         <v>-26.319</v>
       </c>
       <c r="R14" t="n">
-        <v>27.3313</v>
+        <v>27.33130000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.8664</v>
+        <v>-8.841800000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.624000000000001</v>
+        <v>-3.9836</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.242499999999999</v>
+        <v>-4.8582</v>
       </c>
       <c r="V14" t="n">
         <v>-5.3846</v>
